--- a/dataset/construct/dataset_splits/removed_rows/tum_removed_missing_images.xlsx
+++ b/dataset/construct/dataset_splits/removed_rows/tum_removed_missing_images.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,175 +446,160 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>model7</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>model8</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>brand8</t>
         </is>
